--- a/scripts/file_test/test.xlsx
+++ b/scripts/file_test/test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\crm-bank\scripts\file_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2172106A-03A9-46D4-AC61-16D2A3C52AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC71F609-6E86-4B4C-B06D-7D26C9B86F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,13 +54,13 @@
     <t>จำนวนที่ขายรวม</t>
   </si>
   <si>
-    <t>9124D-8400L001-CS1</t>
-  </si>
-  <si>
     <t>DEMO-003</t>
   </si>
   <si>
     <t>HS0101CT</t>
+  </si>
+  <si>
+    <t>9124D-8400L001-CS1dd</t>
   </si>
 </sst>
 </file>
@@ -427,13 +427,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="F3" s="1">
         <v>1000</v>
